--- a/AAII_Financials/Yearly/UNH_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/UNH_YR_FIN.xlsx
@@ -732,7 +732,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>447567000</v>
+        <v>447964000</v>
       </c>
       <c r="E8" s="3">
         <v>400278000</v>
@@ -783,7 +783,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>364650000</v>
+        <v>364027000</v>
       </c>
       <c r="E9" s="3">
         <v>310879000</v>
@@ -834,7 +834,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>82917000</v>
+        <v>83937000</v>
       </c>
       <c r="E10" s="3">
         <v>89399000</v>
@@ -1008,7 +1008,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>265000</v>
+        <v>2685000</v>
       </c>
       <c r="E14" s="3">
         <v>8310000</v>
@@ -1128,7 +1128,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>428603000</v>
+        <v>426580000</v>
       </c>
       <c r="E17" s="3">
         <v>367991000</v>
@@ -1179,7 +1179,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>18964000</v>
+        <v>21384000</v>
       </c>
       <c r="E18" s="3">
         <v>32287000</v>
@@ -1302,7 +1302,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>23325000</v>
+        <v>25745000</v>
       </c>
       <c r="E21" s="3">
         <v>36386000</v>
